--- a/tabular/locus/erv_locus_name_mappings.xlsx
+++ b/tabular/locus/erv_locus_name_mappings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robgifford/Repo/erv/locus/ERVdb-HomoSapiens/tabular/locus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A42DDF-13D1-884D-8AD4-BF426EAEF7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE493290-4B8E-BD47-A18B-925E062A89EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="17080" windowHeight="17480" xr2:uid="{9DD0CFA5-F16B-FC48-804C-24D9B791B390}"/>
+    <workbookView xWindow="1100" yWindow="860" windowWidth="17080" windowHeight="17480" xr2:uid="{9DD0CFA5-F16B-FC48-804C-24D9B791B390}"/>
   </bookViews>
   <sheets>
     <sheet name="erv_locus_name_mappings" sheetId="1" r:id="rId1"/>
@@ -403,7 +403,7 @@
     <t>ervr</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.Lb4</t>
+    <t>ERV-3.Lambda.L.b4</t>
   </si>
 </sst>
 </file>

--- a/tabular/locus/erv_locus_name_mappings.xlsx
+++ b/tabular/locus/erv_locus_name_mappings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robgifford/Repo/erv/locus/ERVdb-HomoSapiens/tabular/locus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE493290-4B8E-BD47-A18B-925E062A89EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9E402-6388-674C-906B-1CD3056B51DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="860" windowWidth="17080" windowHeight="17480" xr2:uid="{9DD0CFA5-F16B-FC48-804C-24D9B791B390}"/>
   </bookViews>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="132">
   <si>
     <t>source_name</t>
   </si>
   <si>
-    <t>candidate_count</t>
-  </si>
-  <si>
     <t>erv_lineage_id</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>MER34A1</t>
   </si>
   <si>
-    <t>PRIMA41</t>
-  </si>
-  <si>
     <t>LTR-43</t>
   </si>
   <si>
@@ -404,6 +398,24 @@
   </si>
   <si>
     <t>ERV-3.Lambda.L.b4</t>
+  </si>
+  <si>
+    <t>PRIMA-41</t>
+  </si>
+  <si>
+    <t>HERV-Rb</t>
+  </si>
+  <si>
+    <t>HERV-Xa</t>
+  </si>
+  <si>
+    <t>HERV-Lb</t>
+  </si>
+  <si>
+    <t>HERV-Lb2</t>
+  </si>
+  <si>
+    <t>HERV-15</t>
   </si>
 </sst>
 </file>
@@ -1313,970 +1325,820 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16641E20-09E5-9446-B119-339FE275C795}">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2">
-        <v>286</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>1011</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4">
-        <v>477</v>
-      </c>
-      <c r="C4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5">
-        <v>348</v>
-      </c>
-      <c r="C5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6">
-        <v>225</v>
-      </c>
-      <c r="C6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7">
-        <v>212</v>
-      </c>
-      <c r="C7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8">
-        <v>302</v>
-      </c>
-      <c r="C8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>2486</v>
-      </c>
-      <c r="C9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>23884</v>
-      </c>
-      <c r="C11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12">
-        <v>418</v>
-      </c>
-      <c r="C12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>25</v>
       </c>
-      <c r="B13">
-        <v>884</v>
-      </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14">
-        <v>1028</v>
-      </c>
-      <c r="C14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15">
-        <v>188</v>
-      </c>
-      <c r="C15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16">
-        <v>540</v>
-      </c>
-      <c r="C16" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17">
-        <v>329</v>
-      </c>
-      <c r="C17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18">
-        <v>202</v>
-      </c>
-      <c r="C18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19">
-        <v>200</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21">
-        <v>537</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22">
-        <v>362</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23">
-        <v>354</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24">
-        <v>312</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25">
-        <v>260</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26">
-        <v>913</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27">
-        <v>607</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28">
-        <v>262</v>
-      </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29">
-        <v>414</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30">
-        <v>218</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31">
-        <v>1063</v>
-      </c>
-      <c r="C31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32">
-        <v>1036</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33">
-        <v>534</v>
-      </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
-        <v>261</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35">
-        <v>1678</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36">
-        <v>1667</v>
-      </c>
-      <c r="C36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>491</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38">
-        <v>2079</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39">
-        <v>188</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40">
-        <v>711</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41">
-        <v>1411</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42">
-        <v>32</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43">
-        <v>92</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44">
-        <v>4051</v>
-      </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>16</v>
       </c>
-      <c r="B45">
-        <v>1445</v>
-      </c>
-      <c r="C45" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="B45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s">
+        <v>102</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46">
-        <v>1530</v>
-      </c>
-      <c r="C46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47">
-        <v>608</v>
-      </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>27</v>
       </c>
-      <c r="B48">
-        <v>662</v>
-      </c>
-      <c r="C48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49">
-        <v>264</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50">
-        <v>336</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51">
-        <v>68</v>
-      </c>
-      <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52">
-        <v>981</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B53">
-        <v>908</v>
-      </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54">
-        <v>593</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55">
-        <v>220</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56">
-        <v>2105</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57">
-        <v>101</v>
-      </c>
-      <c r="C57" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58">
-        <v>1585</v>
-      </c>
-      <c r="C58" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="B68" t="s">
+        <v>110</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>46</v>
       </c>
-      <c r="B59">
-        <v>308</v>
-      </c>
-      <c r="C59" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="B70" t="s">
+        <v>102</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>4</v>
       </c>
-      <c r="B60">
-        <v>12874</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>50</v>
-      </c>
-      <c r="B61">
-        <v>278</v>
-      </c>
-      <c r="C61" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62">
-        <v>448</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63">
-        <v>618</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64">
-        <v>192</v>
-      </c>
-      <c r="C64" t="s">
-        <v>116</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65">
-        <v>292</v>
-      </c>
-      <c r="C65" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66">
-        <v>5002</v>
-      </c>
-      <c r="C66" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="B71" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>102</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>7</v>
       </c>
-      <c r="B67">
-        <v>3404</v>
-      </c>
-      <c r="C67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68">
-        <v>2947</v>
-      </c>
-      <c r="C68" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>127</v>
+      <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D68">
-    <sortCondition ref="C2:C68"/>
-    <sortCondition ref="D2:D68"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C73">
+    <sortCondition ref="B2:B73"/>
+    <sortCondition ref="C2:C73"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tabular/locus/erv_locus_name_mappings.xlsx
+++ b/tabular/locus/erv_locus_name_mappings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robgifford/Repo/erv/locus/ERVdb-HomoSapiens/tabular/locus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF9E402-6388-674C-906B-1CD3056B51DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847DBA15-EBA7-6640-9E71-3F6452115FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="860" windowWidth="17080" windowHeight="17480" xr2:uid="{9DD0CFA5-F16B-FC48-804C-24D9B791B390}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="149">
   <si>
     <t>source_name</t>
   </si>
@@ -388,18 +388,12 @@
     <t>ERVR-3.Lambda.74</t>
   </si>
   <si>
-    <t>ERV-1.Theta.34</t>
-  </si>
-  <si>
     <t>ERVR-1.Zeta.HF.52A</t>
   </si>
   <si>
     <t>ervr</t>
   </si>
   <si>
-    <t>ERV-3.Lambda.L.b4</t>
-  </si>
-  <si>
     <t>PRIMA-41</t>
   </si>
   <si>
@@ -416,6 +410,63 @@
   </si>
   <si>
     <t>HERV-15</t>
+  </si>
+  <si>
+    <t>HERV-K-HML5</t>
+  </si>
+  <si>
+    <t>HERV-K-HML6</t>
+  </si>
+  <si>
+    <t>HERV-K-HML1</t>
+  </si>
+  <si>
+    <t>HERV-K-HML10</t>
+  </si>
+  <si>
+    <t>HERV-K-HML2</t>
+  </si>
+  <si>
+    <t>HERV-K-HML3</t>
+  </si>
+  <si>
+    <t>HERV-K-HML4</t>
+  </si>
+  <si>
+    <t>HERV-K-HML7</t>
+  </si>
+  <si>
+    <t>HERV-K-HML8</t>
+  </si>
+  <si>
+    <t>HERV-K-HML9</t>
+  </si>
+  <si>
+    <t>HERV-Fa</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.HF.Fa.1</t>
+  </si>
+  <si>
+    <t>LOR1</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.LOR1</t>
+  </si>
+  <si>
+    <t>HERV-G25</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.W9P.P.G25</t>
+  </si>
+  <si>
+    <t>PRIMA41</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.L.1.b4</t>
+  </si>
+  <si>
+    <t>ERV-1.Valera.34</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16641E20-09E5-9446-B119-339FE275C795}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1348,7 +1399,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>112</v>
@@ -1359,7 +1410,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>118</v>
@@ -1370,7 +1421,7 @@
         <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>111</v>
@@ -1381,7 +1432,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>104</v>
@@ -1392,7 +1443,7 @@
         <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>105</v>
@@ -1403,7 +1454,7 @@
         <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>108</v>
@@ -1414,7 +1465,7 @@
         <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>116</v>
@@ -1425,10 +1476,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1436,7 +1487,7 @@
         <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>115</v>
@@ -1447,7 +1498,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>117</v>
@@ -1458,7 +1509,7 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>103</v>
@@ -1469,7 +1520,7 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>119</v>
@@ -1480,7 +1531,7 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>107</v>
@@ -1491,7 +1542,7 @@
         <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>121</v>
@@ -1502,7 +1553,7 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>106</v>
@@ -1513,7 +1564,7 @@
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>113</v>
@@ -1524,7 +1575,7 @@
         <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>120</v>
@@ -1543,7 +1594,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
         <v>102</v>
@@ -1642,7 +1693,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
         <v>102</v>
@@ -1692,7 +1743,7 @@
         <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1703,7 +1754,7 @@
         <v>102</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1714,12 +1765,12 @@
         <v>102</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
         <v>102</v>
@@ -1741,7 +1792,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
         <v>102</v>
@@ -1774,7 +1825,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>102</v>
@@ -1785,260 +1836,260 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="B42" t="s">
         <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
         <v>102</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
         <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="B45" t="s">
         <v>102</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
         <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
         <v>102</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
         <v>102</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
         <v>102</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
         <v>102</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B51" t="s">
         <v>102</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
         <v>102</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>79</v>
+      <c r="C54" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
         <v>102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>71</v>
+      <c r="C56" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
         <v>102</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
         <v>102</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>102</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
         <v>102</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
         <v>102</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
         <v>102</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
         <v>102</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
@@ -2049,96 +2100,250 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
         <v>102</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
-      </c>
-      <c r="C68" t="s">
-        <v>27</v>
+        <v>102</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
+      </c>
+      <c r="C70" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="B72" t="s">
         <v>102</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>102</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>7</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B75" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>125</v>
+      <c r="C75" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>132</v>
+      </c>
+      <c r="B78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>138</v>
+      </c>
+      <c r="B84" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>139</v>
+      </c>
+      <c r="B85" t="s">
+        <v>102</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" t="s">
+        <v>123</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>144</v>
+      </c>
+      <c r="B87" t="s">
+        <v>123</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C73">
-    <sortCondition ref="B2:B73"/>
-    <sortCondition ref="C2:C73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C75">
+    <sortCondition ref="B2:B75"/>
+    <sortCondition ref="C2:C75"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
